--- a/artfynd/A 34699-2024 artfynd.xlsx
+++ b/artfynd/A 34699-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419786</v>
+        <v>123419795</v>
       </c>
       <c r="B2" t="n">
-        <v>90969</v>
+        <v>78771</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,31 +691,31 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600572</v>
+        <v>600618</v>
       </c>
       <c r="R2" t="n">
-        <v>6949875</v>
+        <v>6949990</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1910</t>
+          <t>2024_1902</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>4 dm2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419785</v>
+        <v>123419774</v>
       </c>
       <c r="B3" t="n">
-        <v>90955</v>
+        <v>79360</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +826,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,7 +850,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600514</v>
+        <v>600596</v>
       </c>
       <c r="R3" t="n">
-        <v>6949837</v>
+        <v>6949648</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1912</t>
+          <t>2024_1921</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +929,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -935,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419806</v>
+        <v>123419822</v>
       </c>
       <c r="B4" t="n">
-        <v>91400</v>
+        <v>57634</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,25 +952,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -973,21 +978,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600536</v>
+        <v>600256</v>
       </c>
       <c r="R4" t="n">
-        <v>6949941</v>
+        <v>6949649</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1892</t>
+          <t>2024_1876</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419800</v>
+        <v>123419780</v>
       </c>
       <c r="B5" t="n">
-        <v>91400</v>
+        <v>78771</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,25 +1077,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1105,19 +1105,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupsjön, Mpd</t>
+          <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600568</v>
+        <v>600615</v>
       </c>
       <c r="R5" t="n">
-        <v>6949949</v>
+        <v>6949789</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1899</t>
+          <t>2024_1917</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123419795</v>
+        <v>123419785</v>
       </c>
       <c r="B6" t="n">
-        <v>78769</v>
+        <v>90957</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,21 +1211,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1235,7 +1235,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600618</v>
+        <v>600514</v>
       </c>
       <c r="R6" t="n">
-        <v>6949990</v>
+        <v>6949837</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1902</t>
+          <t>2024_1912</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,12 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>4 dm2</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1330,10 +1325,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419820</v>
+        <v>123419818</v>
       </c>
       <c r="B7" t="n">
-        <v>98402</v>
+        <v>78771</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,25 +1337,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1370,7 +1365,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1379,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600284</v>
+        <v>600337</v>
       </c>
       <c r="R7" t="n">
-        <v>6949633</v>
+        <v>6949778</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,7 +1404,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1877</t>
+          <t>2024_1879</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1419,7 +1414,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1429,7 +1424,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1 dm2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1449,7 +1449,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1460,10 +1460,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123419812</v>
+        <v>123419806</v>
       </c>
       <c r="B8" t="n">
-        <v>79387</v>
+        <v>91402</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1472,25 +1472,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600514</v>
+        <v>600536</v>
       </c>
       <c r="R8" t="n">
-        <v>6949878</v>
+        <v>6949941</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1539,7 +1539,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1885</t>
+          <t>2024_1892</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1549,7 +1549,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1559,7 +1559,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1590,10 +1590,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123419780</v>
+        <v>123419786</v>
       </c>
       <c r="B9" t="n">
-        <v>78769</v>
+        <v>90971</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1606,31 +1606,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600615</v>
+        <v>600572</v>
       </c>
       <c r="R9" t="n">
-        <v>6949789</v>
+        <v>6949875</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1917</t>
+          <t>2024_1910</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1720,10 +1720,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123419824</v>
+        <v>123419820</v>
       </c>
       <c r="B10" t="n">
-        <v>98389</v>
+        <v>98404</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1736,16 +1736,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>219874</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600343</v>
+        <v>600284</v>
       </c>
       <c r="R10" t="n">
-        <v>6949578</v>
+        <v>6949633</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1874</t>
+          <t>2024_1877</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1850,10 +1850,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123419792</v>
+        <v>123419812</v>
       </c>
       <c r="B11" t="n">
-        <v>98389</v>
+        <v>79389</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1862,25 +1862,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600569</v>
+        <v>600514</v>
       </c>
       <c r="R11" t="n">
-        <v>6949973</v>
+        <v>6949878</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1905</t>
+          <t>2024_1885</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1980,10 +1980,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123419818</v>
+        <v>123419800</v>
       </c>
       <c r="B12" t="n">
-        <v>78769</v>
+        <v>91402</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1992,25 +1992,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2020,19 +2020,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djupsjön öst om, Mpd</t>
+          <t>Djupsjön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600337</v>
+        <v>600568</v>
       </c>
       <c r="R12" t="n">
-        <v>6949778</v>
+        <v>6949949</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1879</t>
+          <t>2024_1899</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2079,12 +2079,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>1 dm2</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2104,7 +2099,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2115,10 +2110,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123419822</v>
+        <v>123419809</v>
       </c>
       <c r="B13" t="n">
-        <v>57634</v>
+        <v>79360</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2131,21 +2126,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2153,16 +2148,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600256</v>
+        <v>600533</v>
       </c>
       <c r="R13" t="n">
-        <v>6949649</v>
+        <v>6949943</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1876</t>
+          <t>2024_1888</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2240,10 +2240,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123419809</v>
+        <v>123419824</v>
       </c>
       <c r="B14" t="n">
-        <v>79358</v>
+        <v>98391</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2252,35 +2252,35 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600533</v>
+        <v>600343</v>
       </c>
       <c r="R14" t="n">
-        <v>6949943</v>
+        <v>6949578</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1888</t>
+          <t>2024_1874</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2370,10 +2370,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123419774</v>
+        <v>123419792</v>
       </c>
       <c r="B15" t="n">
-        <v>79358</v>
+        <v>98391</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2382,25 +2382,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600596</v>
+        <v>600569</v>
       </c>
       <c r="R15" t="n">
-        <v>6949648</v>
+        <v>6949973</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1921</t>
+          <t>2024_1905</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 34699-2024 artfynd.xlsx
+++ b/artfynd/A 34699-2024 artfynd.xlsx
@@ -2110,10 +2110,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123419809</v>
+        <v>123419824</v>
       </c>
       <c r="B13" t="n">
-        <v>79360</v>
+        <v>98391</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2122,35 +2122,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600533</v>
+        <v>600343</v>
       </c>
       <c r="R13" t="n">
-        <v>6949943</v>
+        <v>6949578</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1888</t>
+          <t>2024_1874</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2240,7 +2240,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123419824</v>
+        <v>123419792</v>
       </c>
       <c r="B14" t="n">
         <v>98391</v>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600343</v>
+        <v>600569</v>
       </c>
       <c r="R14" t="n">
-        <v>6949578</v>
+        <v>6949973</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1874</t>
+          <t>2024_1905</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2370,10 +2370,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123419792</v>
+        <v>123419809</v>
       </c>
       <c r="B15" t="n">
-        <v>98391</v>
+        <v>79360</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2382,25 +2382,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600569</v>
+        <v>600533</v>
       </c>
       <c r="R15" t="n">
-        <v>6949973</v>
+        <v>6949943</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1905</t>
+          <t>2024_1888</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 34699-2024 artfynd.xlsx
+++ b/artfynd/A 34699-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419795</v>
+        <v>123419822</v>
       </c>
       <c r="B2" t="n">
-        <v>78771</v>
+        <v>57634</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,21 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600618</v>
+        <v>600256</v>
       </c>
       <c r="R2" t="n">
-        <v>6949990</v>
+        <v>6949649</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1902</t>
+          <t>2024_1876</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>4 dm2</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419774</v>
+        <v>123419792</v>
       </c>
       <c r="B3" t="n">
-        <v>79360</v>
+        <v>98397</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,25 +812,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -850,7 +840,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600596</v>
+        <v>600569</v>
       </c>
       <c r="R3" t="n">
-        <v>6949648</v>
+        <v>6949973</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +879,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1921</t>
+          <t>2024_1905</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +899,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +919,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -940,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419822</v>
+        <v>123419786</v>
       </c>
       <c r="B4" t="n">
-        <v>57634</v>
+        <v>90977</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -956,26 +946,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600256</v>
+        <v>600572</v>
       </c>
       <c r="R4" t="n">
-        <v>6949649</v>
+        <v>6949875</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1009,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1876</t>
+          <t>2024_1910</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1029,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1049,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1065,10 +1060,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419780</v>
+        <v>123419820</v>
       </c>
       <c r="B5" t="n">
-        <v>78771</v>
+        <v>98410</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,25 +1072,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1105,7 +1100,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1114,10 +1109,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600615</v>
+        <v>600284</v>
       </c>
       <c r="R5" t="n">
-        <v>6949789</v>
+        <v>6949633</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1139,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1917</t>
+          <t>2024_1877</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1149,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1159,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,10 +1190,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123419785</v>
+        <v>123419774</v>
       </c>
       <c r="B6" t="n">
-        <v>90957</v>
+        <v>79361</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1211,21 +1206,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1235,7 +1230,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1244,10 +1239,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600514</v>
+        <v>600596</v>
       </c>
       <c r="R6" t="n">
-        <v>6949837</v>
+        <v>6949648</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1269,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1912</t>
+          <t>2024_1921</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1279,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1289,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1314,7 +1309,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1325,10 +1320,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419818</v>
+        <v>123419824</v>
       </c>
       <c r="B7" t="n">
-        <v>78771</v>
+        <v>98397</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1337,35 +1332,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1374,10 +1369,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600337</v>
+        <v>600343</v>
       </c>
       <c r="R7" t="n">
-        <v>6949778</v>
+        <v>6949578</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,7 +1399,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1879</t>
+          <t>2024_1874</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1414,7 +1409,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1424,12 +1419,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>1 dm2</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1460,10 +1450,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123419806</v>
+        <v>123419818</v>
       </c>
       <c r="B8" t="n">
-        <v>91402</v>
+        <v>78772</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1472,25 +1462,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1500,7 +1490,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1509,10 +1499,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600536</v>
+        <v>600337</v>
       </c>
       <c r="R8" t="n">
-        <v>6949941</v>
+        <v>6949778</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1539,7 +1529,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1892</t>
+          <t>2024_1879</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1549,7 +1539,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1559,7 +1549,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 dm2</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1579,7 +1574,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1590,10 +1585,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123419786</v>
+        <v>123419780</v>
       </c>
       <c r="B9" t="n">
-        <v>90971</v>
+        <v>78772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1606,31 +1601,31 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1639,10 +1634,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600572</v>
+        <v>600615</v>
       </c>
       <c r="R9" t="n">
-        <v>6949875</v>
+        <v>6949789</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1669,7 +1664,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1910</t>
+          <t>2024_1917</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1679,7 +1674,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1689,7 +1684,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1709,7 +1704,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1720,10 +1715,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123419820</v>
+        <v>123419795</v>
       </c>
       <c r="B10" t="n">
-        <v>98404</v>
+        <v>78772</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1732,25 +1727,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1760,7 +1755,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1769,10 +1764,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600284</v>
+        <v>600618</v>
       </c>
       <c r="R10" t="n">
-        <v>6949633</v>
+        <v>6949990</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1799,7 +1794,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1877</t>
+          <t>2024_1902</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1809,7 +1804,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1819,7 +1814,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>4 dm2</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1850,10 +1850,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123419812</v>
+        <v>123419806</v>
       </c>
       <c r="B11" t="n">
-        <v>79389</v>
+        <v>91408</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1862,25 +1862,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1890,7 +1890,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600514</v>
+        <v>600536</v>
       </c>
       <c r="R11" t="n">
-        <v>6949878</v>
+        <v>6949941</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1929,7 +1929,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1885</t>
+          <t>2024_1892</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1939,7 +1939,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1949,7 +1949,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1980,10 +1980,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123419800</v>
+        <v>123419809</v>
       </c>
       <c r="B12" t="n">
-        <v>91402</v>
+        <v>79361</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1992,25 +1992,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>229821</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2020,19 +2020,19 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djupsjön, Mpd</t>
+          <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600568</v>
+        <v>600533</v>
       </c>
       <c r="R12" t="n">
-        <v>6949949</v>
+        <v>6949943</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1899</t>
+          <t>2024_1888</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2110,10 +2110,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123419824</v>
+        <v>123419785</v>
       </c>
       <c r="B13" t="n">
-        <v>98391</v>
+        <v>90963</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2122,35 +2122,35 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600343</v>
+        <v>600514</v>
       </c>
       <c r="R13" t="n">
-        <v>6949578</v>
+        <v>6949837</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1874</t>
+          <t>2024_1912</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2240,10 +2240,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123419792</v>
+        <v>123419812</v>
       </c>
       <c r="B14" t="n">
-        <v>98391</v>
+        <v>79390</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2252,25 +2252,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600569</v>
+        <v>600514</v>
       </c>
       <c r="R14" t="n">
-        <v>6949973</v>
+        <v>6949878</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1905</t>
+          <t>2024_1885</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2370,10 +2370,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123419809</v>
+        <v>123419800</v>
       </c>
       <c r="B15" t="n">
-        <v>79360</v>
+        <v>91408</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2382,25 +2382,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2410,19 +2410,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Djupsjön öst om, Mpd</t>
+          <t>Djupsjön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600533</v>
+        <v>600568</v>
       </c>
       <c r="R15" t="n">
-        <v>6949943</v>
+        <v>6949949</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1888</t>
+          <t>2024_1899</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 34699-2024 artfynd.xlsx
+++ b/artfynd/A 34699-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419822</v>
+        <v>123419824</v>
       </c>
       <c r="B2" t="n">
-        <v>57634</v>
+        <v>98400</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,30 +687,35 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600256</v>
+        <v>600343</v>
       </c>
       <c r="R2" t="n">
-        <v>6949649</v>
+        <v>6949578</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1876</t>
+          <t>2024_1874</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -800,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419792</v>
+        <v>123419812</v>
       </c>
       <c r="B3" t="n">
-        <v>98397</v>
+        <v>79393</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -840,7 +845,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -849,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600569</v>
+        <v>600514</v>
       </c>
       <c r="R3" t="n">
-        <v>6949973</v>
+        <v>6949878</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1905</t>
+          <t>2024_1885</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -899,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -919,7 +924,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -930,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419786</v>
+        <v>123419820</v>
       </c>
       <c r="B4" t="n">
-        <v>90977</v>
+        <v>98413</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,35 +947,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -979,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600572</v>
+        <v>600284</v>
       </c>
       <c r="R4" t="n">
-        <v>6949875</v>
+        <v>6949633</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1910</t>
+          <t>2024_1877</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1019,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1049,7 +1054,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1060,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419820</v>
+        <v>123419774</v>
       </c>
       <c r="B5" t="n">
-        <v>98410</v>
+        <v>79364</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1072,25 +1077,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>229821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1100,7 +1105,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1109,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600284</v>
+        <v>600596</v>
       </c>
       <c r="R5" t="n">
-        <v>6949633</v>
+        <v>6949648</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1139,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1877</t>
+          <t>2024_1921</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1149,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1159,7 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1190,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123419774</v>
+        <v>123419809</v>
       </c>
       <c r="B6" t="n">
-        <v>79361</v>
+        <v>79364</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1239,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600596</v>
+        <v>600533</v>
       </c>
       <c r="R6" t="n">
-        <v>6949648</v>
+        <v>6949943</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1269,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1921</t>
+          <t>2024_1888</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1279,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1289,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1320,10 +1325,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419824</v>
+        <v>123419795</v>
       </c>
       <c r="B7" t="n">
-        <v>98397</v>
+        <v>78775</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1332,35 +1337,35 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1369,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600343</v>
+        <v>600618</v>
       </c>
       <c r="R7" t="n">
-        <v>6949578</v>
+        <v>6949990</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1399,7 +1404,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1874</t>
+          <t>2024_1902</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1409,7 +1414,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1419,7 +1424,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>4 dm2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1450,10 +1460,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123419818</v>
+        <v>123419822</v>
       </c>
       <c r="B8" t="n">
-        <v>78772</v>
+        <v>57634</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1466,21 +1476,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1488,21 +1498,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600337</v>
+        <v>600256</v>
       </c>
       <c r="R8" t="n">
-        <v>6949778</v>
+        <v>6949649</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1529,7 +1534,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1879</t>
+          <t>2024_1876</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1539,7 +1544,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1549,12 +1554,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1 dm2</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1588,7 +1588,7 @@
         <v>123419780</v>
       </c>
       <c r="B9" t="n">
-        <v>78772</v>
+        <v>78775</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1715,10 +1715,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123419795</v>
+        <v>123419800</v>
       </c>
       <c r="B10" t="n">
-        <v>78772</v>
+        <v>91411</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1727,25 +1727,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1755,19 +1755,19 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Djupsjön öst om, Mpd</t>
+          <t>Djupsjön, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600618</v>
+        <v>600568</v>
       </c>
       <c r="R10" t="n">
-        <v>6949990</v>
+        <v>6949949</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1902</t>
+          <t>2024_1899</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1814,12 +1814,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>4 dm2</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1839,7 +1834,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1850,10 +1845,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123419806</v>
+        <v>123419818</v>
       </c>
       <c r="B11" t="n">
-        <v>91408</v>
+        <v>78775</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1862,25 +1857,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1890,7 +1885,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1899,10 +1894,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600536</v>
+        <v>600337</v>
       </c>
       <c r="R11" t="n">
-        <v>6949941</v>
+        <v>6949778</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1929,7 +1924,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1892</t>
+          <t>2024_1879</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1939,7 +1934,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1949,7 +1944,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1 dm2</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1980,10 +1980,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123419809</v>
+        <v>123419786</v>
       </c>
       <c r="B12" t="n">
-        <v>79361</v>
+        <v>90980</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1996,31 +1996,31 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>229821</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2029,10 +2029,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600533</v>
+        <v>600572</v>
       </c>
       <c r="R12" t="n">
-        <v>6949943</v>
+        <v>6949875</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1888</t>
+          <t>2024_1910</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2079,7 +2079,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2099,7 +2099,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2110,10 +2110,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123419785</v>
+        <v>123419806</v>
       </c>
       <c r="B13" t="n">
-        <v>90963</v>
+        <v>91411</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2122,25 +2122,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2159,10 +2159,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600514</v>
+        <v>600536</v>
       </c>
       <c r="R13" t="n">
-        <v>6949837</v>
+        <v>6949941</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1912</t>
+          <t>2024_1892</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2240,10 +2240,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123419812</v>
+        <v>123419785</v>
       </c>
       <c r="B14" t="n">
-        <v>79390</v>
+        <v>90966</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2256,21 +2256,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2292,7 +2292,7 @@
         <v>600514</v>
       </c>
       <c r="R14" t="n">
-        <v>6949878</v>
+        <v>6949837</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1885</t>
+          <t>2024_1912</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2370,10 +2370,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123419800</v>
+        <v>123419792</v>
       </c>
       <c r="B15" t="n">
-        <v>91408</v>
+        <v>98400</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2382,25 +2382,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2410,19 +2410,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Djupsjön, Mpd</t>
+          <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600568</v>
+        <v>600569</v>
       </c>
       <c r="R15" t="n">
-        <v>6949949</v>
+        <v>6949973</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1899</t>
+          <t>2024_1905</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 34699-2024 artfynd.xlsx
+++ b/artfynd/A 34699-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419824</v>
+        <v>123419792</v>
       </c>
       <c r="B2" t="n">
-        <v>98400</v>
+        <v>98417</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600343</v>
+        <v>600569</v>
       </c>
       <c r="R2" t="n">
-        <v>6949578</v>
+        <v>6949973</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1874</t>
+          <t>2024_1905</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419812</v>
+        <v>123419818</v>
       </c>
       <c r="B3" t="n">
-        <v>79393</v>
+        <v>78781</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +821,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -854,10 +854,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600514</v>
+        <v>600337</v>
       </c>
       <c r="R3" t="n">
-        <v>6949878</v>
+        <v>6949778</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1885</t>
+          <t>2024_1879</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1 dm2</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,7 +929,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -935,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419820</v>
+        <v>123419780</v>
       </c>
       <c r="B4" t="n">
-        <v>98413</v>
+        <v>78781</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,25 +952,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -975,7 +980,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600284</v>
+        <v>600615</v>
       </c>
       <c r="R4" t="n">
-        <v>6949633</v>
+        <v>6949789</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1877</t>
+          <t>2024_1917</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1039,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419774</v>
+        <v>123419795</v>
       </c>
       <c r="B5" t="n">
-        <v>79364</v>
+        <v>78781</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1081,21 +1086,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1114,10 +1119,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600596</v>
+        <v>600618</v>
       </c>
       <c r="R5" t="n">
-        <v>6949648</v>
+        <v>6949990</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1149,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1921</t>
+          <t>2024_1902</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1159,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1169,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>4 dm2</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1184,7 +1194,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1195,10 +1205,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123419809</v>
+        <v>123419774</v>
       </c>
       <c r="B6" t="n">
-        <v>79364</v>
+        <v>79370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1244,10 +1254,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600533</v>
+        <v>600596</v>
       </c>
       <c r="R6" t="n">
-        <v>6949943</v>
+        <v>6949648</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1284,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1888</t>
+          <t>2024_1921</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1294,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1304,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1325,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419795</v>
+        <v>123419785</v>
       </c>
       <c r="B7" t="n">
-        <v>78775</v>
+        <v>90983</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1341,21 +1351,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1365,7 +1375,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1374,10 +1384,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600618</v>
+        <v>600514</v>
       </c>
       <c r="R7" t="n">
-        <v>6949990</v>
+        <v>6949837</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,7 +1414,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1902</t>
+          <t>2024_1912</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1414,7 +1424,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1424,12 +1434,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>4 dm2</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1460,10 +1465,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123419822</v>
+        <v>123419812</v>
       </c>
       <c r="B8" t="n">
-        <v>57634</v>
+        <v>79399</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1476,21 +1481,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>6453</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1498,16 +1503,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600256</v>
+        <v>600514</v>
       </c>
       <c r="R8" t="n">
-        <v>6949649</v>
+        <v>6949878</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1534,7 +1544,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1876</t>
+          <t>2024_1885</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1544,7 +1554,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1554,7 +1564,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1585,10 +1595,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123419780</v>
+        <v>123419824</v>
       </c>
       <c r="B9" t="n">
-        <v>78775</v>
+        <v>98417</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1597,35 +1607,35 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1634,10 +1644,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600615</v>
+        <v>600343</v>
       </c>
       <c r="R9" t="n">
-        <v>6949789</v>
+        <v>6949578</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1664,7 +1674,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1917</t>
+          <t>2024_1874</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1674,7 +1684,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1684,7 +1694,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1704,7 +1714,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1715,10 +1725,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123419800</v>
+        <v>123419806</v>
       </c>
       <c r="B10" t="n">
-        <v>91411</v>
+        <v>91428</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1760,14 +1770,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Djupsjön, Mpd</t>
+          <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600568</v>
+        <v>600536</v>
       </c>
       <c r="R10" t="n">
-        <v>6949949</v>
+        <v>6949941</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1794,7 +1804,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1899</t>
+          <t>2024_1892</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1804,7 +1814,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1814,7 +1824,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1845,10 +1855,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123419818</v>
+        <v>123419786</v>
       </c>
       <c r="B11" t="n">
-        <v>78775</v>
+        <v>90997</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1861,31 +1871,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1894,10 +1904,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600337</v>
+        <v>600572</v>
       </c>
       <c r="R11" t="n">
-        <v>6949778</v>
+        <v>6949875</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1924,7 +1934,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1879</t>
+          <t>2024_1910</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1934,7 +1944,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1944,12 +1954,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>1 dm2</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1980,10 +1985,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123419786</v>
+        <v>123419800</v>
       </c>
       <c r="B12" t="n">
-        <v>90980</v>
+        <v>91428</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1992,30 +1997,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2025,14 +2030,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djupsjön öst om, Mpd</t>
+          <t>Djupsjön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600572</v>
+        <v>600568</v>
       </c>
       <c r="R12" t="n">
-        <v>6949875</v>
+        <v>6949949</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2059,7 +2064,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1910</t>
+          <t>2024_1899</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2069,7 +2074,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2079,7 +2084,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2099,7 +2104,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2110,10 +2115,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123419806</v>
+        <v>123419822</v>
       </c>
       <c r="B13" t="n">
-        <v>91411</v>
+        <v>57640</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2122,25 +2127,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2148,21 +2153,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600536</v>
+        <v>600256</v>
       </c>
       <c r="R13" t="n">
-        <v>6949941</v>
+        <v>6949649</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2189,7 +2189,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1892</t>
+          <t>2024_1876</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2209,7 +2209,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2240,10 +2240,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123419785</v>
+        <v>123419820</v>
       </c>
       <c r="B14" t="n">
-        <v>90966</v>
+        <v>98430</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2252,25 +2252,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600514</v>
+        <v>600284</v>
       </c>
       <c r="R14" t="n">
-        <v>6949837</v>
+        <v>6949633</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1912</t>
+          <t>2024_1877</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2370,10 +2370,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123419792</v>
+        <v>123419809</v>
       </c>
       <c r="B15" t="n">
-        <v>98400</v>
+        <v>79370</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2382,25 +2382,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221952</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600569</v>
+        <v>600533</v>
       </c>
       <c r="R15" t="n">
-        <v>6949973</v>
+        <v>6949943</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1905</t>
+          <t>2024_1888</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 34699-2024 artfynd.xlsx
+++ b/artfynd/A 34699-2024 artfynd.xlsx
@@ -1335,10 +1335,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419785</v>
+        <v>123419812</v>
       </c>
       <c r="B7" t="n">
-        <v>90983</v>
+        <v>79399</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1351,21 +1351,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1387,7 +1387,7 @@
         <v>600514</v>
       </c>
       <c r="R7" t="n">
-        <v>6949837</v>
+        <v>6949878</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1912</t>
+          <t>2024_1885</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1465,10 +1465,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123419812</v>
+        <v>123419785</v>
       </c>
       <c r="B8" t="n">
-        <v>79399</v>
+        <v>90983</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1481,21 +1481,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6453</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1517,7 +1517,7 @@
         <v>600514</v>
       </c>
       <c r="R8" t="n">
-        <v>6949878</v>
+        <v>6949837</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1885</t>
+          <t>2024_1912</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1584,7 +1584,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">

--- a/artfynd/A 34699-2024 artfynd.xlsx
+++ b/artfynd/A 34699-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419792</v>
+        <v>123419818</v>
       </c>
       <c r="B2" t="n">
-        <v>98417</v>
+        <v>78786</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,7 +715,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600569</v>
+        <v>600337</v>
       </c>
       <c r="R2" t="n">
-        <v>6949973</v>
+        <v>6949778</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1905</t>
+          <t>2024_1879</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1 dm2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419818</v>
+        <v>123419809</v>
       </c>
       <c r="B3" t="n">
-        <v>78781</v>
+        <v>79375</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,21 +826,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -854,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600337</v>
+        <v>600533</v>
       </c>
       <c r="R3" t="n">
-        <v>6949778</v>
+        <v>6949943</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1879</t>
+          <t>2024_1888</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,12 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1 dm2</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -929,7 +929,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -940,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419780</v>
+        <v>123419785</v>
       </c>
       <c r="B4" t="n">
-        <v>78781</v>
+        <v>90988</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -956,21 +956,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600615</v>
+        <v>600514</v>
       </c>
       <c r="R4" t="n">
-        <v>6949789</v>
+        <v>6949837</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1917</t>
+          <t>2024_1912</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1070,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419795</v>
+        <v>123419822</v>
       </c>
       <c r="B5" t="n">
-        <v>78781</v>
+        <v>57643</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,21 +1086,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1108,21 +1108,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600618</v>
+        <v>600256</v>
       </c>
       <c r="R5" t="n">
-        <v>6949990</v>
+        <v>6949649</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1902</t>
+          <t>2024_1876</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1159,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1169,12 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>4 dm2</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1194,7 +1184,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1205,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123419774</v>
+        <v>123419824</v>
       </c>
       <c r="B6" t="n">
-        <v>79370</v>
+        <v>98523</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1217,35 +1207,35 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1254,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600596</v>
+        <v>600343</v>
       </c>
       <c r="R6" t="n">
-        <v>6949648</v>
+        <v>6949578</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1284,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1921</t>
+          <t>2024_1874</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1294,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1304,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1324,7 +1314,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1338,7 +1328,7 @@
         <v>123419812</v>
       </c>
       <c r="B7" t="n">
-        <v>79399</v>
+        <v>79404</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1465,10 +1455,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123419785</v>
+        <v>123419820</v>
       </c>
       <c r="B8" t="n">
-        <v>90983</v>
+        <v>98536</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1477,25 +1467,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1505,7 +1495,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1514,10 +1504,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600514</v>
+        <v>600284</v>
       </c>
       <c r="R8" t="n">
-        <v>6949837</v>
+        <v>6949633</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1544,7 +1534,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1912</t>
+          <t>2024_1877</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1554,7 +1544,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1564,7 +1554,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1584,7 +1574,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1595,10 +1585,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123419824</v>
+        <v>123419792</v>
       </c>
       <c r="B9" t="n">
-        <v>98417</v>
+        <v>98523</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1630,7 +1620,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1644,10 +1634,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600343</v>
+        <v>600569</v>
       </c>
       <c r="R9" t="n">
-        <v>6949578</v>
+        <v>6949973</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1674,7 +1664,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1874</t>
+          <t>2024_1905</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1684,7 +1674,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1694,7 +1684,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1725,10 +1715,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123419806</v>
+        <v>123419774</v>
       </c>
       <c r="B10" t="n">
-        <v>91428</v>
+        <v>79375</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1737,25 +1727,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1209</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1765,7 +1755,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1774,10 +1764,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600536</v>
+        <v>600596</v>
       </c>
       <c r="R10" t="n">
-        <v>6949941</v>
+        <v>6949648</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1804,7 +1794,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1892</t>
+          <t>2024_1921</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1814,7 +1804,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1824,7 +1814,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1855,10 +1845,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123419786</v>
+        <v>123419780</v>
       </c>
       <c r="B11" t="n">
-        <v>90997</v>
+        <v>78786</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1871,31 +1861,31 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1904,10 +1894,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600572</v>
+        <v>600615</v>
       </c>
       <c r="R11" t="n">
-        <v>6949875</v>
+        <v>6949789</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1934,7 +1924,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1910</t>
+          <t>2024_1917</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1944,7 +1934,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1954,7 +1944,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1974,7 +1964,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1985,10 +1975,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123419800</v>
+        <v>123419786</v>
       </c>
       <c r="B12" t="n">
-        <v>91428</v>
+        <v>91002</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1997,30 +1987,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2030,14 +2020,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djupsjön, Mpd</t>
+          <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600568</v>
+        <v>600572</v>
       </c>
       <c r="R12" t="n">
-        <v>6949949</v>
+        <v>6949875</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2064,7 +2054,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1899</t>
+          <t>2024_1910</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2074,7 +2064,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2084,7 +2074,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2104,7 +2094,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2115,10 +2105,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123419822</v>
+        <v>123419795</v>
       </c>
       <c r="B13" t="n">
-        <v>57640</v>
+        <v>78786</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2131,21 +2121,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2153,16 +2143,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600256</v>
+        <v>600618</v>
       </c>
       <c r="R13" t="n">
-        <v>6949649</v>
+        <v>6949990</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2189,7 +2184,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1876</t>
+          <t>2024_1902</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2199,7 +2194,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2209,7 +2204,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>4 dm2</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2240,10 +2240,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123419820</v>
+        <v>123419806</v>
       </c>
       <c r="B14" t="n">
-        <v>98430</v>
+        <v>91433</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2252,25 +2252,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>219874</v>
+        <v>1209</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600284</v>
+        <v>600536</v>
       </c>
       <c r="R14" t="n">
-        <v>6949633</v>
+        <v>6949941</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1877</t>
+          <t>2024_1892</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2370,10 +2370,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123419809</v>
+        <v>123419800</v>
       </c>
       <c r="B15" t="n">
-        <v>79370</v>
+        <v>91433</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2382,25 +2382,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2410,19 +2410,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Djupsjön öst om, Mpd</t>
+          <t>Djupsjön, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600533</v>
+        <v>600568</v>
       </c>
       <c r="R15" t="n">
-        <v>6949943</v>
+        <v>6949949</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1888</t>
+          <t>2024_1899</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 34699-2024 artfynd.xlsx
+++ b/artfynd/A 34699-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419818</v>
+        <v>123419795</v>
       </c>
       <c r="B2" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600337</v>
+        <v>600618</v>
       </c>
       <c r="R2" t="n">
-        <v>6949778</v>
+        <v>6949990</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1879</t>
+          <t>2024_1902</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1 dm2</t>
+          <t>4 dm2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -810,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419809</v>
+        <v>123419806</v>
       </c>
       <c r="B3" t="n">
-        <v>79375</v>
+        <v>91435</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,25 +822,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600533</v>
+        <v>600536</v>
       </c>
       <c r="R3" t="n">
-        <v>6949943</v>
+        <v>6949941</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -889,7 +889,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1888</t>
+          <t>2024_1892</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -909,7 +909,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -940,10 +940,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419785</v>
+        <v>123419820</v>
       </c>
       <c r="B4" t="n">
-        <v>90988</v>
+        <v>98538</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -952,25 +952,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600514</v>
+        <v>600284</v>
       </c>
       <c r="R4" t="n">
-        <v>6949837</v>
+        <v>6949633</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1019,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1912</t>
+          <t>2024_1877</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,7 +1039,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,7 +1059,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1070,10 +1070,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419822</v>
+        <v>123419785</v>
       </c>
       <c r="B5" t="n">
-        <v>57643</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,21 +1086,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1108,16 +1108,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600256</v>
+        <v>600514</v>
       </c>
       <c r="R5" t="n">
-        <v>6949649</v>
+        <v>6949837</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1149,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1876</t>
+          <t>2024_1912</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1159,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1169,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1184,7 +1189,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1195,10 +1200,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123419824</v>
+        <v>123419792</v>
       </c>
       <c r="B6" t="n">
-        <v>98523</v>
+        <v>98525</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1230,7 +1235,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1244,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600343</v>
+        <v>600569</v>
       </c>
       <c r="R6" t="n">
-        <v>6949578</v>
+        <v>6949973</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1279,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1874</t>
+          <t>2024_1905</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1289,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1299,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1325,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419812</v>
+        <v>123419822</v>
       </c>
       <c r="B7" t="n">
-        <v>79404</v>
+        <v>57644</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1341,21 +1346,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1363,21 +1368,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600514</v>
+        <v>600256</v>
       </c>
       <c r="R7" t="n">
-        <v>6949878</v>
+        <v>6949649</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1885</t>
+          <t>2024_1876</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1455,10 +1455,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123419820</v>
+        <v>123419809</v>
       </c>
       <c r="B8" t="n">
-        <v>98536</v>
+        <v>79377</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1467,25 +1467,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219874</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600284</v>
+        <v>600533</v>
       </c>
       <c r="R8" t="n">
-        <v>6949633</v>
+        <v>6949943</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1877</t>
+          <t>2024_1888</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1585,10 +1585,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123419792</v>
+        <v>123419774</v>
       </c>
       <c r="B9" t="n">
-        <v>98523</v>
+        <v>79377</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1597,25 +1597,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600569</v>
+        <v>600596</v>
       </c>
       <c r="R9" t="n">
-        <v>6949973</v>
+        <v>6949648</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1905</t>
+          <t>2024_1921</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1715,10 +1715,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123419774</v>
+        <v>123419812</v>
       </c>
       <c r="B10" t="n">
-        <v>79375</v>
+        <v>79406</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1731,21 +1731,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600596</v>
+        <v>600514</v>
       </c>
       <c r="R10" t="n">
-        <v>6949648</v>
+        <v>6949878</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1921</t>
+          <t>2024_1885</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1845,10 +1845,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123419780</v>
+        <v>123419824</v>
       </c>
       <c r="B11" t="n">
-        <v>78786</v>
+        <v>98525</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1857,35 +1857,35 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1894,10 +1894,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600615</v>
+        <v>600343</v>
       </c>
       <c r="R11" t="n">
-        <v>6949789</v>
+        <v>6949578</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1917</t>
+          <t>2024_1874</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1934,7 +1934,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1964,7 +1964,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1975,10 +1975,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123419786</v>
+        <v>123419800</v>
       </c>
       <c r="B12" t="n">
-        <v>91002</v>
+        <v>91435</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1987,30 +1987,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2020,14 +2020,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djupsjön öst om, Mpd</t>
+          <t>Djupsjön, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600572</v>
+        <v>600568</v>
       </c>
       <c r="R12" t="n">
-        <v>6949875</v>
+        <v>6949949</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1910</t>
+          <t>2024_1899</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2105,10 +2105,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123419795</v>
+        <v>123419780</v>
       </c>
       <c r="B13" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600618</v>
+        <v>600615</v>
       </c>
       <c r="R13" t="n">
-        <v>6949990</v>
+        <v>6949789</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1902</t>
+          <t>2024_1917</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2204,12 +2204,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>4 dm2</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2229,7 +2224,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2240,10 +2235,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123419806</v>
+        <v>123419786</v>
       </c>
       <c r="B14" t="n">
-        <v>91433</v>
+        <v>91004</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2252,30 +2247,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1209</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2289,10 +2284,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600536</v>
+        <v>600572</v>
       </c>
       <c r="R14" t="n">
-        <v>6949941</v>
+        <v>6949875</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2319,7 +2314,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1892</t>
+          <t>2024_1910</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2329,7 +2324,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2339,7 +2334,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2359,7 +2354,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2370,10 +2365,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123419800</v>
+        <v>123419818</v>
       </c>
       <c r="B15" t="n">
-        <v>91433</v>
+        <v>78788</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2382,25 +2377,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2410,19 +2405,19 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Djupsjön, Mpd</t>
+          <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600568</v>
+        <v>600337</v>
       </c>
       <c r="R15" t="n">
-        <v>6949949</v>
+        <v>6949778</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2449,7 +2444,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1899</t>
+          <t>2024_1879</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2459,7 +2454,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2469,7 +2464,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>1 dm2</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 34699-2024 artfynd.xlsx
+++ b/artfynd/A 34699-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419795</v>
+        <v>123419774</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600618</v>
+        <v>600596</v>
       </c>
       <c r="R2" t="n">
-        <v>6949990</v>
+        <v>6949648</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1902</t>
+          <t>2024_1921</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>4 dm2</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -940,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419820</v>
+        <v>123419824</v>
       </c>
       <c r="B4" t="n">
-        <v>98538</v>
+        <v>98100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -956,16 +951,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>221952</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -975,7 +970,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -989,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600284</v>
+        <v>600343</v>
       </c>
       <c r="R4" t="n">
-        <v>6949633</v>
+        <v>6949578</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1019,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1877</t>
+          <t>2024_1874</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1029,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1039,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1059,7 +1054,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1070,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419785</v>
+        <v>123419812</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>79406</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1086,21 +1081,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1110,7 +1105,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1122,7 +1117,7 @@
         <v>600514</v>
       </c>
       <c r="R5" t="n">
-        <v>6949837</v>
+        <v>6949878</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1149,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1912</t>
+          <t>2024_1885</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1159,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1169,7 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1189,7 +1184,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1200,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123419792</v>
+        <v>123419820</v>
       </c>
       <c r="B6" t="n">
-        <v>98525</v>
+        <v>98113</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1216,16 +1211,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221952</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1249,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600569</v>
+        <v>600284</v>
       </c>
       <c r="R6" t="n">
-        <v>6949973</v>
+        <v>6949633</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1905</t>
+          <t>2024_1877</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1289,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1299,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1319,7 +1314,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1330,10 +1325,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419822</v>
+        <v>123419786</v>
       </c>
       <c r="B7" t="n">
-        <v>57644</v>
+        <v>91004</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1346,26 +1341,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>1204</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600256</v>
+        <v>600572</v>
       </c>
       <c r="R7" t="n">
-        <v>6949649</v>
+        <v>6949875</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1876</t>
+          <t>2024_1910</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1455,10 +1455,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123419809</v>
+        <v>123419785</v>
       </c>
       <c r="B8" t="n">
-        <v>79377</v>
+        <v>90990</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600533</v>
+        <v>600514</v>
       </c>
       <c r="R8" t="n">
-        <v>6949943</v>
+        <v>6949837</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1888</t>
+          <t>2024_1912</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1585,7 +1585,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123419774</v>
+        <v>123419809</v>
       </c>
       <c r="B9" t="n">
         <v>79377</v>
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600596</v>
+        <v>600533</v>
       </c>
       <c r="R9" t="n">
-        <v>6949648</v>
+        <v>6949943</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1921</t>
+          <t>2024_1888</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1715,10 +1715,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123419812</v>
+        <v>123419780</v>
       </c>
       <c r="B10" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1731,21 +1731,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1764,10 +1764,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600514</v>
+        <v>600615</v>
       </c>
       <c r="R10" t="n">
-        <v>6949878</v>
+        <v>6949789</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1885</t>
+          <t>2024_1917</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1814,7 +1814,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1845,10 +1845,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123419824</v>
+        <v>123419822</v>
       </c>
       <c r="B11" t="n">
-        <v>98525</v>
+        <v>57644</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1857,35 +1857,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1894,10 +1889,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600343</v>
+        <v>600256</v>
       </c>
       <c r="R11" t="n">
-        <v>6949578</v>
+        <v>6949649</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1924,7 +1919,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1874</t>
+          <t>2024_1876</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1934,7 +1929,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1944,7 +1939,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1964,7 +1959,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -2105,10 +2100,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123419780</v>
+        <v>123419792</v>
       </c>
       <c r="B13" t="n">
-        <v>78788</v>
+        <v>98100</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2117,25 +2112,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2145,7 +2140,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2154,10 +2149,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600615</v>
+        <v>600569</v>
       </c>
       <c r="R13" t="n">
-        <v>6949789</v>
+        <v>6949973</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2184,7 +2179,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1917</t>
+          <t>2024_1905</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2194,7 +2189,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2204,7 +2199,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2224,7 +2219,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2235,10 +2230,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123419786</v>
+        <v>123419818</v>
       </c>
       <c r="B14" t="n">
-        <v>91004</v>
+        <v>78788</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2251,31 +2246,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2284,10 +2279,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600572</v>
+        <v>600337</v>
       </c>
       <c r="R14" t="n">
-        <v>6949875</v>
+        <v>6949778</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2314,7 +2309,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1910</t>
+          <t>2024_1879</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2324,7 +2319,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2334,7 +2329,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1 dm2</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2365,7 +2365,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123419818</v>
+        <v>123419795</v>
       </c>
       <c r="B15" t="n">
         <v>78788</v>
@@ -2414,10 +2414,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600337</v>
+        <v>600618</v>
       </c>
       <c r="R15" t="n">
-        <v>6949778</v>
+        <v>6949990</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2444,7 +2444,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1879</t>
+          <t>2024_1902</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>1 dm2</t>
+          <t>4 dm2</t>
         </is>
       </c>
       <c r="AD15" t="b">

--- a/artfynd/A 34699-2024 artfynd.xlsx
+++ b/artfynd/A 34699-2024 artfynd.xlsx
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419824</v>
+        <v>123419812</v>
       </c>
       <c r="B4" t="n">
-        <v>98100</v>
+        <v>79406</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -947,35 +947,35 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221952</v>
+        <v>6453</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600343</v>
+        <v>600514</v>
       </c>
       <c r="R4" t="n">
-        <v>6949578</v>
+        <v>6949878</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1874</t>
+          <t>2024_1885</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1065,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419812</v>
+        <v>123419824</v>
       </c>
       <c r="B5" t="n">
-        <v>79406</v>
+        <v>98100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,35 +1077,35 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600514</v>
+        <v>600343</v>
       </c>
       <c r="R5" t="n">
-        <v>6949878</v>
+        <v>6949578</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1885</t>
+          <t>2024_1874</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1455,10 +1455,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123419785</v>
+        <v>123419809</v>
       </c>
       <c r="B8" t="n">
-        <v>90990</v>
+        <v>79377</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1471,21 +1471,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1495,7 +1495,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600514</v>
+        <v>600533</v>
       </c>
       <c r="R8" t="n">
-        <v>6949837</v>
+        <v>6949943</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1912</t>
+          <t>2024_1888</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1585,10 +1585,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123419809</v>
+        <v>123419785</v>
       </c>
       <c r="B9" t="n">
-        <v>79377</v>
+        <v>90990</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1601,21 +1601,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600533</v>
+        <v>600514</v>
       </c>
       <c r="R9" t="n">
-        <v>6949943</v>
+        <v>6949837</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1888</t>
+          <t>2024_1912</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 34699-2024 artfynd.xlsx
+++ b/artfynd/A 34699-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419774</v>
+        <v>123419795</v>
       </c>
       <c r="B2" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -724,10 +724,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600596</v>
+        <v>600618</v>
       </c>
       <c r="R2" t="n">
-        <v>6949648</v>
+        <v>6949990</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1921</t>
+          <t>2024_1902</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>4 dm2</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +799,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,10 +810,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419806</v>
+        <v>123419822</v>
       </c>
       <c r="B3" t="n">
-        <v>91435</v>
+        <v>57644</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +822,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -843,21 +848,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600536</v>
+        <v>600256</v>
       </c>
       <c r="R3" t="n">
-        <v>6949941</v>
+        <v>6949649</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1892</t>
+          <t>2024_1876</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419812</v>
+        <v>123419786</v>
       </c>
       <c r="B4" t="n">
-        <v>79406</v>
+        <v>91004</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,31 +951,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>1204</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600514</v>
+        <v>600572</v>
       </c>
       <c r="R4" t="n">
-        <v>6949878</v>
+        <v>6949875</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1885</t>
+          <t>2024_1910</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1065,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419824</v>
+        <v>123419800</v>
       </c>
       <c r="B5" t="n">
-        <v>98100</v>
+        <v>91435</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,47 +1077,47 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupsjön öst om, Mpd</t>
+          <t>Djupsjön, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600343</v>
+        <v>600568</v>
       </c>
       <c r="R5" t="n">
-        <v>6949578</v>
+        <v>6949949</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1874</t>
+          <t>2024_1899</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1184,7 +1184,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1325,10 +1325,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419786</v>
+        <v>123419806</v>
       </c>
       <c r="B7" t="n">
-        <v>91004</v>
+        <v>91435</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1337,30 +1337,30 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1204</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1374,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600572</v>
+        <v>600536</v>
       </c>
       <c r="R7" t="n">
-        <v>6949875</v>
+        <v>6949941</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,7 +1404,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1910</t>
+          <t>2024_1892</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1424,7 +1424,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1455,7 +1455,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123419809</v>
+        <v>123419774</v>
       </c>
       <c r="B8" t="n">
         <v>79377</v>
@@ -1504,10 +1504,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600533</v>
+        <v>600596</v>
       </c>
       <c r="R8" t="n">
-        <v>6949943</v>
+        <v>6949648</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1888</t>
+          <t>2024_1921</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1585,10 +1585,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123419785</v>
+        <v>123419818</v>
       </c>
       <c r="B9" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1601,21 +1601,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1634,10 +1634,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600514</v>
+        <v>600337</v>
       </c>
       <c r="R9" t="n">
-        <v>6949837</v>
+        <v>6949778</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1664,7 +1664,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1912</t>
+          <t>2024_1879</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1674,7 +1674,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1684,7 +1684,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1 dm2</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1715,10 +1720,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123419780</v>
+        <v>123419812</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>79406</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1731,21 +1736,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1764,10 +1769,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600615</v>
+        <v>600514</v>
       </c>
       <c r="R10" t="n">
-        <v>6949789</v>
+        <v>6949878</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1794,7 +1799,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1917</t>
+          <t>2024_1885</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1804,7 +1809,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1814,7 +1819,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1845,10 +1850,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123419822</v>
+        <v>123419792</v>
       </c>
       <c r="B11" t="n">
-        <v>57644</v>
+        <v>98100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1857,25 +1862,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1883,16 +1888,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600256</v>
+        <v>600569</v>
       </c>
       <c r="R11" t="n">
-        <v>6949649</v>
+        <v>6949973</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1919,7 +1929,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1876</t>
+          <t>2024_1905</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1929,7 +1939,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1939,7 +1949,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1959,7 +1969,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1970,10 +1980,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123419800</v>
+        <v>123419824</v>
       </c>
       <c r="B12" t="n">
-        <v>91435</v>
+        <v>98100</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1982,47 +1992,47 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Djupsjön, Mpd</t>
+          <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600568</v>
+        <v>600343</v>
       </c>
       <c r="R12" t="n">
-        <v>6949949</v>
+        <v>6949578</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2049,7 +2059,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1899</t>
+          <t>2024_1874</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2059,7 +2069,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2069,7 +2079,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2089,7 +2099,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2100,10 +2110,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123419792</v>
+        <v>123419785</v>
       </c>
       <c r="B13" t="n">
-        <v>98100</v>
+        <v>90990</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2112,25 +2122,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2140,7 +2150,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2149,10 +2159,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600569</v>
+        <v>600514</v>
       </c>
       <c r="R13" t="n">
-        <v>6949973</v>
+        <v>6949837</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2179,7 +2189,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1905</t>
+          <t>2024_1912</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2189,7 +2199,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2199,7 +2209,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2230,7 +2240,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123419818</v>
+        <v>123419780</v>
       </c>
       <c r="B14" t="n">
         <v>78788</v>
@@ -2279,10 +2289,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600337</v>
+        <v>600615</v>
       </c>
       <c r="R14" t="n">
-        <v>6949778</v>
+        <v>6949789</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2309,7 +2319,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1879</t>
+          <t>2024_1917</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2319,7 +2329,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2329,12 +2339,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>1 dm2</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2354,7 +2359,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2365,10 +2370,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123419795</v>
+        <v>123419809</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2381,21 +2386,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2414,10 +2419,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600618</v>
+        <v>600533</v>
       </c>
       <c r="R15" t="n">
-        <v>6949990</v>
+        <v>6949943</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2444,7 +2449,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1902</t>
+          <t>2024_1888</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2454,7 +2459,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2464,12 +2469,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>4 dm2</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 34699-2024 artfynd.xlsx
+++ b/artfynd/A 34699-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419795</v>
+        <v>123419800</v>
       </c>
       <c r="B2" t="n">
-        <v>78788</v>
+        <v>91435</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,19 +715,19 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Djupsjön öst om, Mpd</t>
+          <t>Djupsjön, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600618</v>
+        <v>600568</v>
       </c>
       <c r="R2" t="n">
-        <v>6949990</v>
+        <v>6949949</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1902</t>
+          <t>2024_1899</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>4 dm2</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,7 +794,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -810,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419822</v>
+        <v>123419806</v>
       </c>
       <c r="B3" t="n">
-        <v>57644</v>
+        <v>91435</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -822,25 +817,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -848,16 +843,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600256</v>
+        <v>600536</v>
       </c>
       <c r="R3" t="n">
-        <v>6949649</v>
+        <v>6949941</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +884,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1876</t>
+          <t>2024_1892</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419786</v>
+        <v>123419774</v>
       </c>
       <c r="B4" t="n">
-        <v>91004</v>
+        <v>79377</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,31 +951,31 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1204</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -984,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600572</v>
+        <v>600596</v>
       </c>
       <c r="R4" t="n">
-        <v>6949875</v>
+        <v>6949648</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1910</t>
+          <t>2024_1921</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1065,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419800</v>
+        <v>123419818</v>
       </c>
       <c r="B5" t="n">
-        <v>91435</v>
+        <v>78788</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,25 +1077,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1105,19 +1105,19 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Djupsjön, Mpd</t>
+          <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600568</v>
+        <v>600337</v>
       </c>
       <c r="R5" t="n">
-        <v>6949949</v>
+        <v>6949778</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1899</t>
+          <t>2024_1879</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1164,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1 dm2</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1184,7 +1189,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1195,10 +1200,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123419820</v>
+        <v>123419785</v>
       </c>
       <c r="B6" t="n">
-        <v>98113</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1207,25 +1212,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1235,7 +1240,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1244,10 +1249,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600284</v>
+        <v>600514</v>
       </c>
       <c r="R6" t="n">
-        <v>6949633</v>
+        <v>6949837</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1279,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1877</t>
+          <t>2024_1912</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1289,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1299,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1314,7 +1319,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1325,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419806</v>
+        <v>123419812</v>
       </c>
       <c r="B7" t="n">
-        <v>91435</v>
+        <v>79406</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1337,25 +1342,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1365,7 +1370,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1374,10 +1379,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600536</v>
+        <v>600514</v>
       </c>
       <c r="R7" t="n">
-        <v>6949941</v>
+        <v>6949878</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,7 +1409,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1892</t>
+          <t>2024_1885</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1414,7 +1419,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1424,7 +1429,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1455,10 +1460,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123419774</v>
+        <v>123419824</v>
       </c>
       <c r="B8" t="n">
-        <v>79377</v>
+        <v>98100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1467,35 +1472,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1504,10 +1509,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600596</v>
+        <v>600343</v>
       </c>
       <c r="R8" t="n">
-        <v>6949648</v>
+        <v>6949578</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1534,7 +1539,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1921</t>
+          <t>2024_1874</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1544,7 +1549,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1554,7 +1559,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1574,7 +1579,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1585,10 +1590,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123419818</v>
+        <v>123419820</v>
       </c>
       <c r="B9" t="n">
-        <v>78788</v>
+        <v>98113</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1597,25 +1602,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1625,7 +1630,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1634,10 +1639,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600337</v>
+        <v>600284</v>
       </c>
       <c r="R9" t="n">
-        <v>6949778</v>
+        <v>6949633</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1664,7 +1669,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1879</t>
+          <t>2024_1877</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1674,7 +1679,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1684,12 +1689,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>1 dm2</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1709,7 +1709,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
@@ -1720,10 +1720,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123419812</v>
+        <v>123419780</v>
       </c>
       <c r="B10" t="n">
-        <v>79406</v>
+        <v>78788</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1736,21 +1736,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600514</v>
+        <v>600615</v>
       </c>
       <c r="R10" t="n">
-        <v>6949878</v>
+        <v>6949789</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1885</t>
+          <t>2024_1917</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1850,10 +1850,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123419792</v>
+        <v>123419822</v>
       </c>
       <c r="B11" t="n">
-        <v>98100</v>
+        <v>57644</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1862,25 +1862,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221952</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1888,21 +1888,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600569</v>
+        <v>600256</v>
       </c>
       <c r="R11" t="n">
-        <v>6949973</v>
+        <v>6949649</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1929,7 +1924,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1905</t>
+          <t>2024_1876</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1939,7 +1934,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1949,7 +1944,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1969,7 +1964,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1980,7 +1975,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123419824</v>
+        <v>123419792</v>
       </c>
       <c r="B12" t="n">
         <v>98100</v>
@@ -2015,7 +2010,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2029,10 +2024,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600343</v>
+        <v>600569</v>
       </c>
       <c r="R12" t="n">
-        <v>6949578</v>
+        <v>6949973</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2059,7 +2054,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1874</t>
+          <t>2024_1905</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2069,7 +2064,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2079,7 +2074,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2110,10 +2105,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123419785</v>
+        <v>123419809</v>
       </c>
       <c r="B13" t="n">
-        <v>90990</v>
+        <v>79377</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2126,21 +2121,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2150,7 +2145,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2159,10 +2154,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600514</v>
+        <v>600533</v>
       </c>
       <c r="R13" t="n">
-        <v>6949837</v>
+        <v>6949943</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2189,7 +2184,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1912</t>
+          <t>2024_1888</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2199,7 +2194,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2209,7 +2204,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2229,7 +2224,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2240,7 +2235,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123419780</v>
+        <v>123419795</v>
       </c>
       <c r="B14" t="n">
         <v>78788</v>
@@ -2289,10 +2284,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600615</v>
+        <v>600618</v>
       </c>
       <c r="R14" t="n">
-        <v>6949789</v>
+        <v>6949990</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2319,7 +2314,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1917</t>
+          <t>2024_1902</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2329,7 +2324,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2339,7 +2334,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>4 dm2</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2370,10 +2370,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123419809</v>
+        <v>123419786</v>
       </c>
       <c r="B15" t="n">
-        <v>79377</v>
+        <v>91004</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2386,31 +2386,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600533</v>
+        <v>600572</v>
       </c>
       <c r="R15" t="n">
-        <v>6949943</v>
+        <v>6949875</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1888</t>
+          <t>2024_1910</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 34699-2024 artfynd.xlsx
+++ b/artfynd/A 34699-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419800</v>
+        <v>123419822</v>
       </c>
       <c r="B2" t="n">
-        <v>91435</v>
+        <v>57644</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,21 +713,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Djupsjön, Mpd</t>
+          <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600568</v>
+        <v>600256</v>
       </c>
       <c r="R2" t="n">
-        <v>6949949</v>
+        <v>6949649</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1899</t>
+          <t>2024_1876</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +800,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419806</v>
+        <v>123419774</v>
       </c>
       <c r="B3" t="n">
-        <v>91435</v>
+        <v>79377</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,25 +812,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1209</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -845,7 +840,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +849,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600536</v>
+        <v>600596</v>
       </c>
       <c r="R3" t="n">
-        <v>6949941</v>
+        <v>6949648</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +879,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1892</t>
+          <t>2024_1921</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +889,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +899,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,10 +930,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419774</v>
+        <v>123419818</v>
       </c>
       <c r="B4" t="n">
-        <v>79377</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -951,21 +946,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -984,10 +979,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600596</v>
+        <v>600337</v>
       </c>
       <c r="R4" t="n">
-        <v>6949648</v>
+        <v>6949778</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +1009,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1921</t>
+          <t>2024_1879</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1019,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1029,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1 dm2</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1065,10 +1065,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419818</v>
+        <v>123419792</v>
       </c>
       <c r="B5" t="n">
-        <v>78788</v>
+        <v>98100</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1077,25 +1077,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1114,10 +1114,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600337</v>
+        <v>600569</v>
       </c>
       <c r="R5" t="n">
-        <v>6949778</v>
+        <v>6949973</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1879</t>
+          <t>2024_1905</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1154,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,12 +1164,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1 dm2</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1200,10 +1195,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123419785</v>
+        <v>123419780</v>
       </c>
       <c r="B6" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1216,21 +1211,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1240,7 +1235,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1249,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600514</v>
+        <v>600615</v>
       </c>
       <c r="R6" t="n">
-        <v>6949837</v>
+        <v>6949789</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1279,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1912</t>
+          <t>2024_1917</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1289,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1299,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1319,7 +1314,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1330,10 +1325,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419812</v>
+        <v>123419820</v>
       </c>
       <c r="B7" t="n">
-        <v>79406</v>
+        <v>98113</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1342,25 +1337,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>219874</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1370,7 +1365,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1379,10 +1374,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600514</v>
+        <v>600284</v>
       </c>
       <c r="R7" t="n">
-        <v>6949878</v>
+        <v>6949633</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1409,7 +1404,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1885</t>
+          <t>2024_1877</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1419,7 +1414,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1429,7 +1424,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1460,10 +1455,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123419824</v>
+        <v>123419795</v>
       </c>
       <c r="B8" t="n">
-        <v>98100</v>
+        <v>78788</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1472,35 +1467,35 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1509,10 +1504,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600343</v>
+        <v>600618</v>
       </c>
       <c r="R8" t="n">
-        <v>6949578</v>
+        <v>6949990</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1539,7 +1534,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1874</t>
+          <t>2024_1902</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1549,7 +1544,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1559,7 +1554,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>4 dm2</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1590,10 +1590,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123419820</v>
+        <v>123419812</v>
       </c>
       <c r="B9" t="n">
-        <v>98113</v>
+        <v>79406</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1602,25 +1602,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219874</v>
+        <v>6453</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600284</v>
+        <v>600514</v>
       </c>
       <c r="R9" t="n">
-        <v>6949633</v>
+        <v>6949878</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1669,7 +1669,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1877</t>
+          <t>2024_1885</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1689,7 +1689,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1720,10 +1720,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123419780</v>
+        <v>123419824</v>
       </c>
       <c r="B10" t="n">
-        <v>78788</v>
+        <v>98100</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1732,35 +1732,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221952</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1769,10 +1769,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600615</v>
+        <v>600343</v>
       </c>
       <c r="R10" t="n">
-        <v>6949789</v>
+        <v>6949578</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1799,7 +1799,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1917</t>
+          <t>2024_1874</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1819,7 +1819,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1850,10 +1850,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123419822</v>
+        <v>123419800</v>
       </c>
       <c r="B11" t="n">
-        <v>57644</v>
+        <v>91435</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1862,25 +1862,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>1209</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1888,16 +1888,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupsjön öst om, Mpd</t>
+          <t>Djupsjön, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600256</v>
+        <v>600568</v>
       </c>
       <c r="R11" t="n">
-        <v>6949649</v>
+        <v>6949949</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1924,7 +1929,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1876</t>
+          <t>2024_1899</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1934,7 +1939,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1944,7 +1949,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1975,10 +1980,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123419792</v>
+        <v>123419785</v>
       </c>
       <c r="B12" t="n">
-        <v>98100</v>
+        <v>90990</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1987,25 +1992,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2015,7 +2020,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2024,10 +2029,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600569</v>
+        <v>600514</v>
       </c>
       <c r="R12" t="n">
-        <v>6949973</v>
+        <v>6949837</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2054,7 +2059,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1905</t>
+          <t>2024_1912</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2064,7 +2069,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2074,7 +2079,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2105,10 +2110,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123419809</v>
+        <v>123419806</v>
       </c>
       <c r="B13" t="n">
-        <v>79377</v>
+        <v>91435</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2117,25 +2122,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>1209</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2145,7 +2150,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2154,10 +2159,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600533</v>
+        <v>600536</v>
       </c>
       <c r="R13" t="n">
-        <v>6949943</v>
+        <v>6949941</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2184,7 +2189,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1888</t>
+          <t>2024_1892</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2194,7 +2199,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2204,7 +2209,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2235,10 +2240,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123419795</v>
+        <v>123419786</v>
       </c>
       <c r="B14" t="n">
-        <v>78788</v>
+        <v>91004</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2251,31 +2256,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2284,10 +2289,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600618</v>
+        <v>600572</v>
       </c>
       <c r="R14" t="n">
-        <v>6949990</v>
+        <v>6949875</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2314,7 +2319,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1902</t>
+          <t>2024_1910</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2324,7 +2329,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2334,12 +2339,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>4 dm2</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2370,10 +2370,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123419786</v>
+        <v>123419809</v>
       </c>
       <c r="B15" t="n">
-        <v>91004</v>
+        <v>79377</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2386,31 +2386,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600572</v>
+        <v>600533</v>
       </c>
       <c r="R15" t="n">
-        <v>6949875</v>
+        <v>6949943</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1910</t>
+          <t>2024_1888</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 34699-2024 artfynd.xlsx
+++ b/artfynd/A 34699-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419822</v>
+        <v>123419780</v>
       </c>
       <c r="B2" t="n">
-        <v>57644</v>
+        <v>78788</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -713,16 +713,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600256</v>
+        <v>600615</v>
       </c>
       <c r="R2" t="n">
-        <v>6949649</v>
+        <v>6949789</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,7 +754,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1876</t>
+          <t>2024_1917</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -759,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +774,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -930,10 +935,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419818</v>
+        <v>123419809</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>79377</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -946,21 +951,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -979,10 +984,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600337</v>
+        <v>600533</v>
       </c>
       <c r="R4" t="n">
-        <v>6949778</v>
+        <v>6949943</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1009,7 +1014,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1879</t>
+          <t>2024_1888</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1019,7 +1024,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1029,12 +1034,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1 dm2</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1195,7 +1195,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123419780</v>
+        <v>123419818</v>
       </c>
       <c r="B6" t="n">
         <v>78788</v>
@@ -1244,10 +1244,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600615</v>
+        <v>600337</v>
       </c>
       <c r="R6" t="n">
-        <v>6949789</v>
+        <v>6949778</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1274,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1917</t>
+          <t>2024_1879</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1294,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1 dm2</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1314,7 +1319,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1325,10 +1330,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419820</v>
+        <v>123419800</v>
       </c>
       <c r="B7" t="n">
-        <v>98113</v>
+        <v>91435</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1337,25 +1342,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219874</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1365,19 +1370,19 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Djupsjön öst om, Mpd</t>
+          <t>Djupsjön, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600284</v>
+        <v>600568</v>
       </c>
       <c r="R7" t="n">
-        <v>6949633</v>
+        <v>6949949</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,7 +1409,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1877</t>
+          <t>2024_1899</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1414,7 +1419,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1424,7 +1429,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1455,10 +1460,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123419795</v>
+        <v>123419820</v>
       </c>
       <c r="B8" t="n">
-        <v>78788</v>
+        <v>98113</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1467,25 +1472,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1495,7 +1500,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1504,10 +1509,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600618</v>
+        <v>600284</v>
       </c>
       <c r="R8" t="n">
-        <v>6949990</v>
+        <v>6949633</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1534,7 +1539,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1902</t>
+          <t>2024_1877</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1544,7 +1549,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1554,12 +1559,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>4 dm2</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1590,10 +1590,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123419812</v>
+        <v>123419822</v>
       </c>
       <c r="B9" t="n">
-        <v>79406</v>
+        <v>57644</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1606,21 +1606,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6453</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1628,21 +1628,16 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600514</v>
+        <v>600256</v>
       </c>
       <c r="R9" t="n">
-        <v>6949878</v>
+        <v>6949649</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1669,7 +1664,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1885</t>
+          <t>2024_1876</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1679,7 +1674,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1689,7 +1684,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1720,10 +1715,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123419824</v>
+        <v>123419785</v>
       </c>
       <c r="B10" t="n">
-        <v>98100</v>
+        <v>90990</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1732,35 +1727,35 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221952</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1769,10 +1764,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600343</v>
+        <v>600514</v>
       </c>
       <c r="R10" t="n">
-        <v>6949578</v>
+        <v>6949837</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1799,7 +1794,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1874</t>
+          <t>2024_1912</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1809,7 +1804,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1819,7 +1814,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1850,10 +1845,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123419800</v>
+        <v>123419824</v>
       </c>
       <c r="B11" t="n">
-        <v>91435</v>
+        <v>98100</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1862,47 +1857,47 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1209</v>
+        <v>221952</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Djupsjön, Mpd</t>
+          <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600568</v>
+        <v>600343</v>
       </c>
       <c r="R11" t="n">
-        <v>6949949</v>
+        <v>6949578</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1929,7 +1924,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1899</t>
+          <t>2024_1874</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1939,7 +1934,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1949,7 +1944,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1969,7 +1964,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1980,10 +1975,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123419785</v>
+        <v>123419795</v>
       </c>
       <c r="B12" t="n">
-        <v>90990</v>
+        <v>78788</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1996,21 +1991,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2020,7 +2015,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2029,10 +2024,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600514</v>
+        <v>600618</v>
       </c>
       <c r="R12" t="n">
-        <v>6949837</v>
+        <v>6949990</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2059,7 +2054,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1912</t>
+          <t>2024_1902</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2069,7 +2064,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2079,7 +2074,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>4 dm2</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2240,10 +2240,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123419786</v>
+        <v>123419812</v>
       </c>
       <c r="B14" t="n">
-        <v>91004</v>
+        <v>79406</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2256,31 +2256,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2289,10 +2289,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600572</v>
+        <v>600514</v>
       </c>
       <c r="R14" t="n">
-        <v>6949875</v>
+        <v>6949878</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1910</t>
+          <t>2024_1885</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2339,7 +2339,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
@@ -2370,10 +2370,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123419809</v>
+        <v>123419786</v>
       </c>
       <c r="B15" t="n">
-        <v>79377</v>
+        <v>91004</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2386,31 +2386,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2419,10 +2419,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600533</v>
+        <v>600572</v>
       </c>
       <c r="R15" t="n">
-        <v>6949943</v>
+        <v>6949875</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2449,7 +2449,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1888</t>
+          <t>2024_1910</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2469,7 +2469,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">

--- a/artfynd/A 34699-2024 artfynd.xlsx
+++ b/artfynd/A 34699-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123419800</v>
+        <v>123419785</v>
       </c>
       <c r="B2" t="n">
-        <v>91457</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -720,14 +715,14 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Djupsjön, Mpd</t>
+          <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>600568</v>
+        <v>600514</v>
       </c>
       <c r="R2" t="n">
-        <v>6949949</v>
+        <v>6949837</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,7 +749,7 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>2024_1899</t>
+          <t>2024_1912</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -764,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,7 +789,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -805,47 +800,42 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123419824</v>
+        <v>123419786</v>
       </c>
       <c r="B3" t="n">
-        <v>98122</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221952</v>
+        <v>1204</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -854,10 +844,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>600343</v>
+        <v>600572</v>
       </c>
       <c r="R3" t="n">
-        <v>6949578</v>
+        <v>6949875</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -884,7 +874,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>2024_1874</t>
+          <t>2024_1910</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -894,7 +884,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +894,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>10:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -935,15 +925,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123419812</v>
+        <v>123419800</v>
       </c>
       <c r="B4" t="n">
-        <v>79428</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -951,21 +936,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -975,19 +960,19 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Djupsjön öst om, Mpd</t>
+          <t>Djupsjön, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>600514</v>
+        <v>600568</v>
       </c>
       <c r="R4" t="n">
-        <v>6949878</v>
+        <v>6949949</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1014,7 +999,7 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>2024_1885</t>
+          <t>2024_1899</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
@@ -1024,7 +1009,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1034,7 +1019,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>08:56</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1065,15 +1050,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123419780</v>
+        <v>123419806</v>
       </c>
       <c r="B5" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1081,21 +1061,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1105,7 +1085,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1114,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>600615</v>
+        <v>600536</v>
       </c>
       <c r="R5" t="n">
-        <v>6949789</v>
+        <v>6949941</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1144,7 +1124,7 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>2024_1917</t>
+          <t>2024_1892</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1154,7 +1134,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1164,7 +1144,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1195,37 +1175,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123419774</v>
+        <v>123419780</v>
       </c>
       <c r="B6" t="n">
-        <v>79399</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1244,10 +1219,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>600596</v>
+        <v>600615</v>
       </c>
       <c r="R6" t="n">
-        <v>6949648</v>
+        <v>6949789</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1274,7 +1249,7 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>2024_1921</t>
+          <t>2024_1917</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1284,7 +1259,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1294,7 +1269,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:51</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1325,15 +1300,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123419806</v>
+        <v>123419795</v>
       </c>
       <c r="B7" t="n">
-        <v>91457</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,21 +1311,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1365,7 +1335,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1374,10 +1344,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>600536</v>
+        <v>600618</v>
       </c>
       <c r="R7" t="n">
-        <v>6949941</v>
+        <v>6949990</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1404,7 +1374,7 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2024_1892</t>
+          <t>2024_1902</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1414,7 +1384,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1424,7 +1394,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>09:42</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>4 dm2</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1444,7 +1419,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1455,37 +1430,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123419785</v>
+        <v>123419818</v>
       </c>
       <c r="B8" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1495,7 +1465,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1504,10 +1474,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>600514</v>
+        <v>600337</v>
       </c>
       <c r="R8" t="n">
-        <v>6949837</v>
+        <v>6949778</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1534,7 +1504,7 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>2024_1912</t>
+          <t>2024_1879</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1544,7 +1514,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1554,7 +1524,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>08:42</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1 dm2</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1585,15 +1560,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>123419822</v>
+        <v>123419773</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1601,21 +1571,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6437</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1623,16 +1593,21 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Djupsjön öst om, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>600256</v>
+        <v>600586</v>
       </c>
       <c r="R9" t="n">
-        <v>6949649</v>
+        <v>6949633</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1659,7 +1634,7 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>2024_1876</t>
+          <t>2024_1922</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
@@ -1669,7 +1644,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1679,7 +1654,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>08:38</t>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1710,37 +1685,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>123419820</v>
+        <v>123419812</v>
       </c>
       <c r="B10" t="n">
-        <v>98135</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>219874</v>
+        <v>6453</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1750,7 +1720,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1759,10 +1729,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>600284</v>
+        <v>600514</v>
       </c>
       <c r="R10" t="n">
-        <v>6949633</v>
+        <v>6949878</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1789,7 +1759,7 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>2024_1877</t>
+          <t>2024_1885</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
@@ -1799,7 +1769,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1809,7 +1779,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>08:39</t>
+          <t>08:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1840,15 +1810,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>123419786</v>
+        <v>123419822</v>
       </c>
       <c r="B11" t="n">
-        <v>91026</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1856,31 +1821,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1204</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1889,10 +1849,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>600572</v>
+        <v>600256</v>
       </c>
       <c r="R11" t="n">
-        <v>6949875</v>
+        <v>6949649</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1919,7 +1879,7 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2024_1910</t>
+          <t>2024_1876</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
@@ -1929,7 +1889,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1939,7 +1899,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:31</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1959,7 +1919,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
@@ -1970,37 +1930,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>123419795</v>
+        <v>123419820</v>
       </c>
       <c r="B12" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>219874</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -2010,7 +1965,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -2019,10 +1974,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>600618</v>
+        <v>600284</v>
       </c>
       <c r="R12" t="n">
-        <v>6949990</v>
+        <v>6949633</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2049,7 +2004,7 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2024_1902</t>
+          <t>2024_1877</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -2059,7 +2014,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2069,12 +2024,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:42</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>4 dm2</t>
+          <t>08:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2094,7 +2044,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
@@ -2105,37 +2055,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>123419809</v>
+        <v>123419792</v>
       </c>
       <c r="B13" t="n">
-        <v>79399</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>221952</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -2145,7 +2090,7 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2154,10 +2099,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>600533</v>
+        <v>600569</v>
       </c>
       <c r="R13" t="n">
-        <v>6949943</v>
+        <v>6949973</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2184,7 +2129,7 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>2024_1888</t>
+          <t>2024_1905</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2194,7 +2139,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2204,7 +2149,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:03</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2224,7 +2169,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Douglas Skarp</t>
+          <t>Felix Gunnarsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
@@ -2235,15 +2180,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123419792</v>
+        <v>123419824</v>
       </c>
       <c r="B14" t="n">
-        <v>98122</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2270,7 +2210,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2284,10 +2224,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>600569</v>
+        <v>600343</v>
       </c>
       <c r="R14" t="n">
-        <v>6949973</v>
+        <v>6949578</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2314,7 +2254,7 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>2024_1905</t>
+          <t>2024_1874</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2324,7 +2264,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2334,7 +2274,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:51</t>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2365,15 +2305,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123419818</v>
+        <v>123419774</v>
       </c>
       <c r="B15" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79917</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2381,21 +2316,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -2414,10 +2349,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>600337</v>
+        <v>600596</v>
       </c>
       <c r="R15" t="n">
-        <v>6949778</v>
+        <v>6949648</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2444,7 +2379,7 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>2024_1879</t>
+          <t>2024_1921</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
@@ -2454,7 +2389,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>08:42</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2464,12 +2399,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>08:42</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>1 dm2</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2489,10 +2419,135 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Felix Gunnarsson</t>
+          <t>Douglas Skarp</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
+        <is>
+          <t>Kustpaketet</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123419809</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Djupsjön öst om, Mpd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>600533</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6949943</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Indal</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2024_1888</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-08-20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>David Isaksson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Douglas Skarp</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
         <is>
           <t>Kustpaketet</t>
         </is>

--- a/artfynd/A 34699-2024 artfynd.xlsx
+++ b/artfynd/A 34699-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -797,6 +802,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419785</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -922,6 +932,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419786</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1047,6 +1062,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419800</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1172,6 +1192,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419806</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1297,6 +1322,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419780</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1427,6 +1457,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419795</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1557,6 +1592,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419818</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1682,6 +1722,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419773</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1807,6 +1852,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419812</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1927,6 +1977,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419822</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2052,6 +2107,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419820</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2177,6 +2237,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419792</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2302,6 +2367,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419824</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2427,6 +2497,11 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419774</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2552,8 +2627,30 @@
           <t>Kustpaketet</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123419809</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>